--- a/ARM Functions/Other Mechanics/Check for not twice in a row moves.xlsx
+++ b/ARM Functions/Other Mechanics/Check for not twice in a row moves.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Other Mechanics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE5630B-7227-4FAA-A51F-215D50E39984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC01A24E-EB1F-422D-986D-DE9EFFA5B392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
@@ -131,9 +131,6 @@
     <t>cmp r0, r5</t>
   </si>
   <si>
-    <t>st r1 to "can't use twice in a row" bit (using F24 in pk3ds)</t>
-  </si>
-  <si>
     <t>0500A0E1</t>
   </si>
   <si>
@@ -207,6 +204,9 @@
   </si>
   <si>
     <t>03D8FEEA</t>
+  </si>
+  <si>
+    <t>"can't use twice in a row" bit (using F24 in pk3ds)</t>
   </si>
 </sst>
 </file>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" s="2" t="str">
         <f>_xlfn.CONCAT("bne 0x",A10)</f>
@@ -716,10 +716,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>9</v>
@@ -734,13 +734,13 @@
         <v>000DD258</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -749,7 +749,7 @@
         <v>000DD25C</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>11</v>
@@ -762,7 +762,7 @@
         <v>000DD260</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>12</v>
@@ -775,7 +775,7 @@
         <v>000DD264</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" s="5" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$5)</f>
@@ -791,7 +791,7 @@
         <v>000DD268</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>18</v>
@@ -806,7 +806,7 @@
         <v>000DD26C</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>29</v>
@@ -821,7 +821,7 @@
         <v>000DD270</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>30</v>
@@ -836,7 +836,7 @@
         <v>000DD274</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="7" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$5)</f>
@@ -850,7 +850,7 @@
         <v>000DD278</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>15</v>
@@ -865,7 +865,7 @@
         <v>000DD27C</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C20" s="4" t="str">
         <f>_xlfn.CONCAT("beq 0x",A7)</f>
@@ -879,13 +879,13 @@
         <v>000DD280</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -894,10 +894,10 @@
         <v>000DD284</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D22" s="6"/>
     </row>
@@ -907,7 +907,7 @@
         <v>000DD288</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>19</v>
@@ -920,7 +920,7 @@
         <v>000DD28C</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>17</v>
@@ -933,13 +933,13 @@
         <v>000DD290</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -948,7 +948,7 @@
         <v>000DD294</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>19</v>
@@ -961,7 +961,7 @@
         <v>000DD298</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>20</v>
@@ -974,7 +974,7 @@
         <v>000DD29C</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C28" s="2" t="str">
         <f>_xlfn.CONCAT("b 0x",A7)</f>
@@ -986,7 +986,7 @@
     </row>
     <row r="33" spans="4:4">
       <c r="D33" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
